--- a/data/trans_camb/POLIPATOLOGIA_5-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Edad-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,09</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,26</t>
+          <t>0,0; 0,24</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,21</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,65</t>
+          <t>0,53; 5,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,77</t>
+          <t>0,0; 0,78</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,59</t>
+          <t>0,0; 0,71</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,54</t>
+          <t>0,24; 2,5</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 0,46</t>
+          <t>-0,27; 0,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,0</t>
+          <t>-0,68; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 0,97</t>
+          <t>-2,12; 0,82</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,6</t>
+          <t>-2,29; 0,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 2,63</t>
+          <t>-0,99; 2,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,44</t>
+          <t>-0,95; 0,42</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,27</t>
+          <t>-1,09; 0,28</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 1,85</t>
+          <t>-0,21; 1,81</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,31; 147,78</t>
+          <t>-80,61; 93,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 86,32</t>
+          <t>-82,65; 79,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-47,67; 241,25</t>
+          <t>-41,28; 315,04</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-79,13; 106,45</t>
+          <t>-75,8; 103,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-85,2; 67,09</t>
+          <t>-82,81; 74,08</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,19; 332,77</t>
+          <t>-22,37; 339,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 0,44</t>
+          <t>-1,26; 0,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,38</t>
+          <t>-1,29; 0,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 4,36</t>
+          <t>0,98; 4,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 2,77</t>
+          <t>-0,39; 2,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 1,81</t>
+          <t>-1,27; 1,84</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 4,18</t>
+          <t>0,61; 4,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 1,39</t>
+          <t>-0,57; 1,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 0,79</t>
+          <t>-0,96; 0,74</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 3,89</t>
+          <t>1,3; 3,77</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 241,81</t>
+          <t>-100,0; 196,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 165,18</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,13; 1299,18</t>
+          <t>49,3; 1293,62</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-22,53; 227,58</t>
+          <t>-21,33; 235,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 149,42</t>
+          <t>-47,3; 144,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>14,78; 323,44</t>
+          <t>18,34; 316,53</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-32,02; 141,92</t>
+          <t>-29,36; 120,33</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,48; 80,38</t>
+          <t>-54,07; 75,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62,91; 373,09</t>
+          <t>63,46; 394,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 1,77</t>
+          <t>-1,85; 1,8</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 2,29</t>
+          <t>-1,56; 1,97</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 5,41</t>
+          <t>-1,35; 5,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 4,12</t>
+          <t>-1,83; 4,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 4,82</t>
+          <t>-1,07; 4,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,16</t>
+          <t>4,79; 11,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,04; 2,44</t>
+          <t>-1,08; 2,43</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,93</t>
+          <t>-0,48; 2,88</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,12; 7,33</t>
+          <t>1,3; 7,43</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,86; 145,18</t>
+          <t>-59,29; 187,67</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,73; 213,97</t>
+          <t>-52,73; 155,27</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-17,01; 384,39</t>
+          <t>-28,12; 441,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-26,43; 111,67</t>
+          <t>-28,27; 116,79</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-16,32; 129,86</t>
+          <t>-17,42; 122,2</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>65,04; 295,36</t>
+          <t>69,07; 309,62</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 90,71</t>
+          <t>-24,41; 88,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-14,09; 109,82</t>
+          <t>-12,36; 108,37</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>39,75; 263,29</t>
+          <t>32,3; 250,84</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,81; 1,32</t>
+          <t>-5,3; 0,99</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 2,36</t>
+          <t>-4,17; 2,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,69; 8,18</t>
+          <t>1,4; 8,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,41; 9,82</t>
+          <t>0,38; 10,04</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0,65; 10,37</t>
+          <t>1,06; 9,92</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,46; 12,54</t>
+          <t>5,07; 12,74</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 4,67</t>
+          <t>-0,99; 4,72</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 5,2</t>
+          <t>-0,52; 5,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,18; 9,44</t>
+          <t>4,19; 9,63</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-63,25; 32,67</t>
+          <t>-64,87; 24,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-52,98; 59,59</t>
+          <t>-53,71; 45,3</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17,48; 193,26</t>
+          <t>11,45; 188,83</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,95; 116,13</t>
+          <t>2,84; 119,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>3,31; 121,53</t>
+          <t>7,89; 121,74</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>32,82; 155,43</t>
+          <t>36,29; 164,77</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 64,53</t>
+          <t>-10,36; 67,2</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,24; 75,28</t>
+          <t>-5,43; 79,13</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>41,63; 138,81</t>
+          <t>43,27; 141,7</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 7,52</t>
+          <t>-3,34; 7,74</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,86; 0,58</t>
+          <t>-8,18; 1,09</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,42</t>
+          <t>-1,74; 7,65</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 8,65</t>
+          <t>-2,75; 9,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,13; 12,27</t>
+          <t>0,53; 12,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,99; 63,27</t>
+          <t>10,28; 62,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,91</t>
+          <t>-1,43; 6,89</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 5,27</t>
+          <t>-2,48; 5,45</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,51; 52,61</t>
+          <t>6,0; 52,36</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,8; 73,83</t>
+          <t>-24,61; 79,17</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,86; 12,16</t>
+          <t>-56,51; 13,55</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-14,08; 79,92</t>
+          <t>-12,96; 79,31</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-14,0; 61,01</t>
+          <t>-13,76; 65,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,09; 83,43</t>
+          <t>1,54; 91,56</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56,25; 445,83</t>
+          <t>56,17; 464,63</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-9,05; 52,76</t>
+          <t>-8,64; 53,18</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-13,18; 40,67</t>
+          <t>-15,17; 41,63</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>42,19; 399,25</t>
+          <t>37,16; 373,3</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 11,3</t>
+          <t>-3,88; 11,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 7,45</t>
+          <t>-5,31; 8,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,38; 22,78</t>
+          <t>9,42; 22,66</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,41; 20,02</t>
+          <t>5,36; 19,49</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 12,71</t>
+          <t>-2,0; 12,51</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>18,73; 31,12</t>
+          <t>19,28; 31,18</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>4,3; 14,46</t>
+          <t>3,98; 14,22</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 8,97</t>
+          <t>-0,92; 9,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17,68; 26,06</t>
+          <t>17,02; 25,85</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,63; 80,6</t>
+          <t>-20,35; 79,14</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-29,18; 54,43</t>
+          <t>-26,06; 65,71</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>42,79; 177,29</t>
+          <t>46,61; 183,28</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>19,89; 106,16</t>
+          <t>20,17; 103,47</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-5,88; 68,25</t>
+          <t>-7,16; 64,9</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>67,53; 169,5</t>
+          <t>71,67; 166,26</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>18,61; 81,39</t>
+          <t>17,52; 81,99</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 49,79</t>
+          <t>-4,28; 49,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>76,17; 149,63</t>
+          <t>72,11; 146,11</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 1,28</t>
+          <t>-0,56; 1,35</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 0,95</t>
+          <t>-0,78; 1,03</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,82; 5,77</t>
+          <t>2,78; 5,8</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,41</t>
+          <t>1,87; 4,54</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,66; 4,49</t>
+          <t>1,81; 4,62</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,92; 29,05</t>
+          <t>8,93; 28,94</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,59</t>
+          <t>0,95; 2,62</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,41</t>
+          <t>0,82; 2,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,48; 18,45</t>
+          <t>6,57; 17,29</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 44,02</t>
+          <t>-15,15; 45,52</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,1; 30,97</t>
+          <t>-20,25; 34,15</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>78,76; 191,5</t>
+          <t>78,94; 196,21</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>24,02; 71,98</t>
+          <t>25,54; 75,25</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>21,43; 73,04</t>
+          <t>23,98; 74,54</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>127,37; 449,22</t>
+          <t>128,89; 452,83</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,33; 54,18</t>
+          <t>16,94; 56,79</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>13,87; 51,36</t>
+          <t>14,34; 51,64</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>124,87; 367,06</t>
+          <t>126,3; 341,95</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/POLIPATOLOGIA_5-Edad-trans_camb.xlsx
+++ b/data/trans_camb/POLIPATOLOGIA_5-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,42</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03</t>
+          <t>1,85</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,09</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -687,37 +687,37 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,24</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,15</t>
+          <t>0,0; 1,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 1,26</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 5,8</t>
+          <t>0,56; 5,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,78</t>
+          <t>0,0; 0,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,71</t>
+          <t>0,0; 0,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,24; 2,5</t>
+          <t>0,28; 2,61</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,43</t>
+          <t>0,4</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,72</t>
+          <t>1,04</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,73</t>
+          <t>0,82</t>
         </is>
       </c>
     </row>
@@ -893,37 +893,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,27; 0,46</t>
+          <t>-0,29; 0,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 0,0</t>
+          <t>-0,69; 0,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,66</t>
+          <t>-0,16; 1,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,82</t>
+          <t>-2,08; 0,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 0,61</t>
+          <t>-2,09; 0,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 2,84</t>
+          <t>-0,83; 2,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 0,42</t>
+          <t>-0,96; 0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 1,81</t>
+          <t>-0,18; 1,8</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>315,22%</t>
+          <t>294,77%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>91,51%</t>
         </is>
       </c>
     </row>
@@ -1014,32 +1014,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-80,61; 93,91</t>
+          <t>-79,11; 125,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-82,65; 79,67</t>
+          <t>-81,83; 107,69</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 315,04</t>
+          <t>-37,84; 257,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 103,28</t>
+          <t>-79,2; 113,35</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 74,08</t>
+          <t>-83,48; 67,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-22,37; 339,06</t>
+          <t>-20,38; 325,23</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,5</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,77</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>2,44</t>
+          <t>2,49</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 0,36</t>
+          <t>-1,32; 0,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,36</t>
+          <t>-1,42; 0,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,34</t>
+          <t>0,78; 4,21</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 2,95</t>
+          <t>-0,71; 2,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,27; 1,84</t>
+          <t>-1,18; 1,76</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 4,1</t>
+          <t>1,09; 4,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,23</t>
+          <t>-0,54; 1,33</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,74</t>
+          <t>-0,99; 0,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,77</t>
+          <t>1,33; 3,69</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>315,59%</t>
+          <t>283,84%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>118,6%</t>
+          <t>138,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>171,89%</t>
+          <t>175,37%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 196,18</t>
+          <t>-94,61; 311,17</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 165,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49,3; 1293,62</t>
+          <t>20,42; 1188,78</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,33; 235,25</t>
+          <t>-27,31; 218,81</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-47,3; 144,3</t>
+          <t>-42,7; 122,59</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>18,34; 316,53</t>
+          <t>36,45; 372,83</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-29,36; 120,33</t>
+          <t>-31,84; 127,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-54,07; 75,55</t>
+          <t>-51,86; 74,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63,46; 394,98</t>
+          <t>65,29; 398,06</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>4,41</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,01</t>
+          <t>7,78</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>6,18</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,85; 1,8</t>
+          <t>-1,97; 1,63</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,97</t>
+          <t>-1,68; 2,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 5,54</t>
+          <t>2,09; 6,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,39</t>
+          <t>-1,25; 4,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,07; 4,59</t>
+          <t>-0,94; 4,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,79; 11,29</t>
+          <t>4,85; 10,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,43</t>
+          <t>-0,96; 2,47</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,88</t>
+          <t>-0,49; 2,87</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,43</t>
+          <t>4,35; 7,99</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>125,22%</t>
+          <t>208,77%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>156,29%</t>
+          <t>151,74%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>134,91%</t>
+          <t>171,0%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 187,67</t>
+          <t>-65,2; 147,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,73; 155,27</t>
+          <t>-52,92; 179,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-28,12; 441,0</t>
+          <t>52,21; 569,75</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 116,79</t>
+          <t>-20,47; 117,27</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 122,2</t>
+          <t>-16,21; 126,42</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>69,07; 309,62</t>
+          <t>65,87; 283,81</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-24,41; 88,0</t>
+          <t>-22,54; 90,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-12,36; 108,37</t>
+          <t>-11,0; 102,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>32,3; 250,84</t>
+          <t>95,3; 308,93</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5,03</t>
+          <t>4,76</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,94</t>
+          <t>8,77</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6,89</t>
+          <t>6,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,99</t>
+          <t>-5,12; 1,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,06</t>
+          <t>-4,18; 2,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,4; 8,27</t>
+          <t>1,08; 8,02</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,38; 10,04</t>
+          <t>1,07; 10,08</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,06; 9,92</t>
+          <t>1,16; 10,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,07; 12,74</t>
+          <t>4,78; 12,46</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 4,72</t>
+          <t>-0,97; 5,02</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 5,24</t>
+          <t>-0,48; 5,12</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>4,19; 9,63</t>
+          <t>4,02; 9,11</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>85,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>81,48%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-64,87; 24,12</t>
+          <t>-66,4; 23,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-53,71; 45,3</t>
+          <t>-54,73; 48,7</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>11,45; 188,83</t>
+          <t>7,93; 175,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2,84; 119,73</t>
+          <t>5,07; 118,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>7,89; 121,74</t>
+          <t>9,22; 130,83</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>36,29; 164,77</t>
+          <t>36,22; 156,95</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 67,2</t>
+          <t>-10,71; 77,29</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 79,13</t>
+          <t>-6,42; 76,81</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>43,27; 141,7</t>
+          <t>38,72; 128,78</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,98</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35,83</t>
+          <t>12,49</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>23,83</t>
+          <t>7,43</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 7,74</t>
+          <t>-3,69; 7,63</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,18; 1,09</t>
+          <t>-8,48; 0,71</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 7,65</t>
+          <t>-2,7; 6,37</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 9,18</t>
+          <t>-2,74; 9,04</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,53; 12,99</t>
+          <t>0,63; 12,99</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10,28; 62,8</t>
+          <t>7,31; 17,15</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 6,89</t>
+          <t>-1,81; 6,34</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 5,45</t>
+          <t>-1,95; 5,29</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6,0; 52,36</t>
+          <t>3,83; 11,11</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>212,1%</t>
+          <t>73,94%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>161,76%</t>
+          <t>50,43%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-24,61; 79,17</t>
+          <t>-26,55; 74,04</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-56,51; 13,55</t>
+          <t>-56,79; 9,89</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-12,96; 79,31</t>
+          <t>-17,93; 72,38</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-13,76; 65,2</t>
+          <t>-14,22; 60,79</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,54; 91,56</t>
+          <t>1,32; 89,79</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>56,17; 464,63</t>
+          <t>36,68; 125,36</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-8,64; 53,18</t>
+          <t>-10,52; 48,78</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-15,17; 41,63</t>
+          <t>-11,38; 40,5</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>37,16; 373,3</t>
+          <t>22,57; 90,22</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>16,46</t>
+          <t>16,28</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>25,13</t>
+          <t>25,04</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>21,59</t>
+          <t>21,45</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,88; 11,06</t>
+          <t>-3,39; 10,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,31; 8,41</t>
+          <t>-4,72; 8,03</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>9,42; 22,66</t>
+          <t>8,91; 23,13</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>5,36; 19,49</t>
+          <t>5,47; 19,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 12,51</t>
+          <t>-1,91; 12,27</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>19,28; 31,18</t>
+          <t>18,94; 30,55</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,98; 14,22</t>
+          <t>3,57; 14,11</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 9,16</t>
+          <t>-0,6; 8,76</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>17,02; 25,85</t>
+          <t>17,16; 26,32</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>110,72%</t>
+          <t>110,33%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>105,63%</t>
+          <t>104,94%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-20,35; 79,14</t>
+          <t>-18,07; 75,98</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-26,06; 65,71</t>
+          <t>-23,63; 59,77</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>46,61; 183,28</t>
+          <t>41,19; 178,94</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>20,17; 103,47</t>
+          <t>19,25; 107,57</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-7,16; 64,9</t>
+          <t>-7,18; 64,88</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>71,67; 166,26</t>
+          <t>68,9; 163,65</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>17,52; 81,99</t>
+          <t>15,51; 79,93</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-4,28; 49,75</t>
+          <t>-3,02; 49,42</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>72,11; 146,11</t>
+          <t>72,22; 151,06</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>4,54</t>
+          <t>4,98</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>13,99</t>
+          <t>9,68</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>9,47</t>
+          <t>7,42</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,35</t>
+          <t>-0,53; 1,33</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 1,03</t>
+          <t>-0,85; 0,98</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2,78; 5,8</t>
+          <t>3,94; 6,02</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1,87; 4,54</t>
+          <t>1,84; 4,54</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,62</t>
+          <t>1,67; 4,55</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>8,93; 28,94</t>
+          <t>8,51; 11,04</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,62</t>
+          <t>0,97; 2,59</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,82; 2,48</t>
+          <t>0,81; 2,48</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>6,57; 17,29</t>
+          <t>6,55; 8,28</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>133,07%</t>
+          <t>145,98%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>208,71%</t>
+          <t>144,44%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>186,19%</t>
+          <t>145,95%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-15,15; 45,52</t>
+          <t>-13,54; 45,07</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 34,15</t>
+          <t>-22,21; 31,12</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>78,94; 196,21</t>
+          <t>100,2; 199,14</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>25,54; 75,25</t>
+          <t>24,72; 74,38</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,98; 74,54</t>
+          <t>22,99; 75,2</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>128,89; 452,83</t>
+          <t>113,29; 181,88</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>16,94; 56,79</t>
+          <t>17,67; 54,64</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>14,34; 51,64</t>
+          <t>14,82; 52,58</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>126,3; 341,95</t>
+          <t>119,33; 179,06</t>
         </is>
       </c>
     </row>
